--- a/resolveIssues/ig/StructureDefinition-fr-lm-quantity-exposure.xlsx
+++ b/resolveIssues/ig/StructureDefinition-fr-lm-quantity-exposure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:56:38+00:00</t>
+    <t>2026-06-04T08:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/resolveIssues/ig/StructureDefinition-fr-lm-quantity-exposure.xlsx
+++ b/resolveIssues/ig/StructureDefinition-fr-lm-quantity-exposure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T08:54:45+00:00</t>
+    <t>2026-06-04T14:47:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
